--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>WSL2</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Snowflake / BigQuery</t>
+  </si>
+  <si>
+    <t>AI (LLM) Code Debugging</t>
   </si>
 </sst>
 </file>
@@ -456,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
@@ -497,7 +500,7 @@
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -574,6 +577,11 @@
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9615"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9285" windowHeight="3690"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
@@ -522,45 +522,43 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -578,11 +576,15 @@
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="B19" s="5"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9285" windowHeight="3690"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9615"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>Great Expectations &gt;&gt;&gt; (Idempotency)</t>
   </si>
   <si>
-    <t>PostgreSQL &gt;&gt;&gt; (Star Schemas)</t>
-  </si>
-  <si>
     <t>Airflow</t>
   </si>
   <si>
@@ -74,6 +71,9 @@
   </si>
   <si>
     <t>AI (LLM) Code Debugging</t>
+  </si>
+  <si>
+    <t>PostgreSQL &gt;&gt;&gt; (Star Schemas  (Kimball Method))</t>
   </si>
 </sst>
 </file>
@@ -492,7 +492,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3"/>
     </row>
@@ -530,7 +530,7 @@
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -540,41 +540,41 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="5"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="5"/>
     </row>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -28,15 +28,9 @@
     <t>VS Code</t>
   </si>
   <si>
-    <t>Docker</t>
-  </si>
-  <si>
     <t>GitHub</t>
   </si>
   <si>
-    <t>Scrapy</t>
-  </si>
-  <si>
     <t>Scrapy-Playwright</t>
   </si>
   <si>
@@ -46,12 +40,6 @@
     <t>DBeaver</t>
   </si>
   <si>
-    <t>dbt</t>
-  </si>
-  <si>
-    <t>Great Expectations &gt;&gt;&gt; (Idempotency)</t>
-  </si>
-  <si>
     <t>Airflow</t>
   </si>
   <si>
@@ -74,6 +62,18 @@
   </si>
   <si>
     <t>PostgreSQL &gt;&gt;&gt; (Star Schemas  (Kimball Method))</t>
+  </si>
+  <si>
+    <t>Great Expectations</t>
+  </si>
+  <si>
+    <t>dbt &gt;&gt;&gt; (Idempotency)</t>
+  </si>
+  <si>
+    <t>Scrapy &gt;&gt;&gt; (Scalability)</t>
+  </si>
+  <si>
+    <t>Docker &gt;&gt;&gt; (Avoid Dependency Hell)</t>
   </si>
 </sst>
 </file>
@@ -486,25 +486,25 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3"/>
     </row>
@@ -516,71 +516,72 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" s="5"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B19" s="5"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -536,7 +536,7 @@
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>WSL2</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Docker &gt;&gt;&gt; (Avoid Dependency Hell)</t>
+  </si>
+  <si>
+    <t>GitHub Actions (CI/CD)</t>
   </si>
 </sst>
 </file>
@@ -488,7 +491,7 @@
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -530,7 +533,7 @@
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -542,7 +545,7 @@
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="4"/>
+      <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -552,9 +555,9 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -583,6 +586,12 @@
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -49,9 +49,6 @@
     <t>Spark</t>
   </si>
   <si>
-    <t>Azure</t>
-  </si>
-  <si>
     <t>Kubernetes</t>
   </si>
   <si>
@@ -67,16 +64,19 @@
     <t>Great Expectations</t>
   </si>
   <si>
-    <t>dbt &gt;&gt;&gt; (Idempotency)</t>
-  </si>
-  <si>
     <t>Scrapy &gt;&gt;&gt; (Scalability)</t>
   </si>
   <si>
     <t>Docker &gt;&gt;&gt; (Avoid Dependency Hell)</t>
   </si>
   <si>
-    <t>GitHub Actions (CI/CD)</t>
+    <t>dbt &gt;&gt;&gt; (Idempotency) &gt;&gt;&gt; (Medallion Architecture)</t>
+  </si>
+  <si>
+    <t>GitHub Actions &gt;&gt;&gt; (CI/CD)</t>
+  </si>
+  <si>
+    <t>AWS &gt;&gt;&gt; (DevOps)</t>
   </si>
 </sst>
 </file>
@@ -113,13 +113,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,13 +489,13 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2"/>
     </row>
@@ -519,7 +519,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -531,13 +531,13 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3"/>
     </row>
@@ -549,15 +549,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="B15" s="5"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -568,19 +568,19 @@
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="5"/>
+      <c r="B17" s="4"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="4"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="B19" s="4"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -589,12 +589,12 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" s="3"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="5"/>
+      <c r="B22" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -92,7 +92,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -114,12 +114,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -151,13 +145,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,7 +550,7 @@
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="5"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -484,7 +484,7 @@
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -550,7 +550,7 @@
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>WSL2</t>
   </si>
@@ -31,9 +31,6 @@
     <t>GitHub</t>
   </si>
   <si>
-    <t>Scrapy-Playwright</t>
-  </si>
-  <si>
     <t>SQL</t>
   </si>
   <si>
@@ -41,21 +38,6 @@
   </si>
   <si>
     <t>Airflow</t>
-  </si>
-  <si>
-    <t>Java</t>
-  </si>
-  <si>
-    <t>Spark</t>
-  </si>
-  <si>
-    <t>Kubernetes</t>
-  </si>
-  <si>
-    <t>Snowflake / BigQuery</t>
-  </si>
-  <si>
-    <t>AI (LLM) Code Debugging</t>
   </si>
   <si>
     <t>PostgreSQL &gt;&gt;&gt; (Star Schemas  (Kimball Method))</t>
@@ -482,19 +464,19 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2"/>
     </row>
@@ -512,79 +494,69 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A17" s="4"/>
       <c r="B17" s="4"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A18" s="4"/>
       <c r="B18" s="4"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="A19" s="4"/>
       <c r="B19" s="4"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="3"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -40,25 +40,25 @@
     <t>Airflow</t>
   </si>
   <si>
-    <t>PostgreSQL &gt;&gt;&gt; (Star Schemas  (Kimball Method))</t>
-  </si>
-  <si>
     <t>Great Expectations</t>
   </si>
   <si>
-    <t>Scrapy &gt;&gt;&gt; (Scalability)</t>
-  </si>
-  <si>
-    <t>Docker &gt;&gt;&gt; (Avoid Dependency Hell)</t>
-  </si>
-  <si>
-    <t>dbt &gt;&gt;&gt; (Idempotency) &gt;&gt;&gt; (Medallion Architecture)</t>
-  </si>
-  <si>
-    <t>GitHub Actions &gt;&gt;&gt; (CI/CD)</t>
-  </si>
-  <si>
-    <t>AWS &gt;&gt;&gt; (DevOps)</t>
+    <t>dbt (Idempotency + Medallion Architecture)</t>
+  </si>
+  <si>
+    <t>Scrapy (Scalability)</t>
+  </si>
+  <si>
+    <t>PostgreSQL (Star Schemas)</t>
+  </si>
+  <si>
+    <t>Docker (Avoid Dependency Hell)</t>
+  </si>
+  <si>
+    <t>GitHub Actions (CI/CD)</t>
+  </si>
+  <si>
+    <t>AWS (DevOps)</t>
   </si>
 </sst>
 </file>
@@ -464,13 +464,13 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2"/>
     </row>
@@ -506,13 +506,13 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="3"/>
     </row>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -484,7 +484,7 @@
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -496,7 +496,7 @@
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -508,7 +508,7 @@
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -74,7 +74,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -84,12 +84,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -127,12 +121,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,7 +483,7 @@
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -514,7 +507,7 @@
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="2"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -535,31 +528,31 @@
       <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="4"/>
+      <c r="B22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
